--- a/reports/hourly_tracking.xlsx
+++ b/reports/hourly_tracking.xlsx
@@ -176,7 +176,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -199,7 +199,7 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>10336</v>
+        <v>10870</v>
       </c>
     </row>
     <row r="12">
@@ -221,7 +221,7 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>705 (6.8%)</t>
+          <t>728 (6.7%)</t>
         </is>
       </c>
     </row>
@@ -233,7 +233,7 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>9 of 456</t>
+          <t>8 of 480</t>
         </is>
       </c>
     </row>
@@ -245,7 +245,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>1.26 (1.00 = independent arrivals)</t>
+          <t>1.25 (1.00 = independent arrivals)</t>
         </is>
       </c>
     </row>
@@ -2076,86 +2076,173 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="C21" s="2">
+        <v>534</v>
+      </c>
+      <c r="D21" s="2">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2">
+        <v>11</v>
+      </c>
+      <c r="F21" s="2">
+        <v>18</v>
+      </c>
+      <c r="G21" s="2">
+        <v>18</v>
+      </c>
+      <c r="H21" s="2">
+        <v>19</v>
+      </c>
+      <c r="I21" s="2">
+        <v>54</v>
+      </c>
+      <c r="J21" s="2">
+        <v>50</v>
+      </c>
+      <c r="K21" s="2">
+        <v>38</v>
+      </c>
+      <c r="L21" s="2">
+        <v>44</v>
+      </c>
+      <c r="M21" s="2">
+        <v>32</v>
+      </c>
+      <c r="N21" s="2">
+        <v>25</v>
+      </c>
+      <c r="O21" s="2">
+        <v>10</v>
+      </c>
+      <c r="P21" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>21</v>
+      </c>
+      <c r="R21" s="2">
+        <v>17</v>
+      </c>
+      <c r="S21" s="2">
+        <v>24</v>
+      </c>
+      <c r="T21" s="2">
+        <v>22</v>
+      </c>
+      <c r="U21" s="2">
+        <v>21</v>
+      </c>
+      <c r="V21" s="2">
+        <v>23</v>
+      </c>
+      <c r="W21" s="2">
+        <v>17</v>
+      </c>
+      <c r="X21" s="2">
+        <v>6</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>13</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5">
-        <v>10336</v>
-      </c>
-      <c r="D21" s="5">
-        <v>265</v>
-      </c>
-      <c r="E21" s="5">
+      <c r="B22" s="4"/>
+      <c r="C22" s="5">
+        <v>10870</v>
+      </c>
+      <c r="D22" s="5">
+        <v>280</v>
+      </c>
+      <c r="E22" s="5">
+        <v>301</v>
+      </c>
+      <c r="F22" s="5">
         <v>290</v>
       </c>
-      <c r="F21" s="5">
-        <v>272</v>
-      </c>
-      <c r="G21" s="5">
-        <v>331</v>
-      </c>
-      <c r="H21" s="5">
-        <v>572</v>
-      </c>
-      <c r="I21" s="5">
-        <v>899</v>
-      </c>
-      <c r="J21" s="5">
-        <v>991</v>
-      </c>
-      <c r="K21" s="5">
-        <v>798</v>
-      </c>
-      <c r="L21" s="5">
-        <v>767</v>
-      </c>
-      <c r="M21" s="5">
-        <v>564</v>
-      </c>
-      <c r="N21" s="5">
-        <v>512</v>
-      </c>
-      <c r="O21" s="5">
-        <v>443</v>
-      </c>
-      <c r="P21" s="5">
-        <v>361</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>312</v>
-      </c>
-      <c r="R21" s="5">
-        <v>363</v>
-      </c>
-      <c r="S21" s="5">
-        <v>331</v>
-      </c>
-      <c r="T21" s="5">
+      <c r="G22" s="5">
+        <v>349</v>
+      </c>
+      <c r="H22" s="5">
+        <v>591</v>
+      </c>
+      <c r="I22" s="5">
+        <v>953</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1041</v>
+      </c>
+      <c r="K22" s="5">
+        <v>836</v>
+      </c>
+      <c r="L22" s="5">
+        <v>811</v>
+      </c>
+      <c r="M22" s="5">
+        <v>596</v>
+      </c>
+      <c r="N22" s="5">
+        <v>537</v>
+      </c>
+      <c r="O22" s="5">
+        <v>453</v>
+      </c>
+      <c r="P22" s="5">
+        <v>381</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>333</v>
+      </c>
+      <c r="R22" s="5">
+        <v>380</v>
+      </c>
+      <c r="S22" s="5">
+        <v>355</v>
+      </c>
+      <c r="T22" s="5">
+        <v>433</v>
+      </c>
+      <c r="U22" s="5">
         <v>411</v>
       </c>
-      <c r="U21" s="5">
-        <v>390</v>
-      </c>
-      <c r="V21" s="5">
-        <v>281</v>
-      </c>
-      <c r="W21" s="5">
-        <v>287</v>
-      </c>
-      <c r="X21" s="5">
-        <v>203</v>
-      </c>
-      <c r="Y21" s="5">
-        <v>224</v>
-      </c>
-      <c r="Z21" s="5">
-        <v>235</v>
-      </c>
-      <c r="AA21" s="5">
-        <v>234</v>
+      <c r="V22" s="5">
+        <v>304</v>
+      </c>
+      <c r="W22" s="5">
+        <v>304</v>
+      </c>
+      <c r="X22" s="5">
+        <v>209</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>232</v>
+      </c>
+      <c r="Z22" s="5">
+        <v>248</v>
+      </c>
+      <c r="AA22" s="5">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3922,83 +4009,167 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="C21" s="3">
+        <v>0.028089887640449437</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.020599250936329586</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.033707865168539325</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.033707865168539325</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.035580524344569285</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.10112359550561797</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.09363295880149813</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.07116104868913857</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.08239700374531835</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0.0599250936329588</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0.04681647940074907</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0.018726591760299626</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0.03745318352059925</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0.03932584269662921</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0.031835205992509365</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0.04119850187265917</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0.03932584269662921</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0.04307116104868914</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0.031835205992509365</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0.0149812734082397</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>0.024344569288389514</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0.0149812734082397</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5">
-        <v>0.025638544891640868</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.028057275541795667</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0.02631578947368421</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0.03202399380804954</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0.055340557275541796</v>
-      </c>
-      <c r="H21" s="5">
-        <v>0.08697755417956657</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0.09587848297213622</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0.07720588235294118</v>
-      </c>
-      <c r="K21" s="5">
-        <v>0.07420665634674922</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0.05456656346749226</v>
-      </c>
-      <c r="M21" s="5">
-        <v>0.04953560371517028</v>
-      </c>
-      <c r="N21" s="5">
-        <v>0.042859907120743036</v>
-      </c>
-      <c r="O21" s="5">
-        <v>0.034926470588235295</v>
-      </c>
-      <c r="P21" s="5">
-        <v>0.03018575851393189</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>0.03511996904024768</v>
-      </c>
-      <c r="R21" s="5">
-        <v>0.03202399380804954</v>
-      </c>
-      <c r="S21" s="5">
-        <v>0.03976393188854489</v>
-      </c>
-      <c r="T21" s="5">
-        <v>0.03773219814241486</v>
-      </c>
-      <c r="U21" s="5">
-        <v>0.02718653250773994</v>
-      </c>
-      <c r="V21" s="5">
-        <v>0.02776702786377709</v>
-      </c>
-      <c r="W21" s="5">
-        <v>0.019640092879256967</v>
-      </c>
-      <c r="X21" s="5">
-        <v>0.021671826625386997</v>
-      </c>
-      <c r="Y21" s="5">
-        <v>0.022736068111455107</v>
-      </c>
-      <c r="Z21" s="5">
-        <v>0.022639318885448918</v>
+      <c r="B22" s="4"/>
+      <c r="C22" s="5">
+        <v>0.025758969641214352</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.027690892364305428</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.02667893284268629</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.03210671573137074</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.05436982520699172</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0.08767249310027599</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.09576816927322906</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0.07690892364305428</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0.07460901563937443</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.05482980680772769</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0.04940202391904324</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0.04167433302667893</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0.035050597976080955</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0.03063477460901564</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0.034958601655933765</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0.03265869365225391</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0.03983440662373505</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0.03781048758049678</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0.02796688132474701</v>
+      </c>
+      <c r="V22" s="5">
+        <v>0.02796688132474701</v>
+      </c>
+      <c r="W22" s="5">
+        <v>0.01922723091076357</v>
+      </c>
+      <c r="X22" s="5">
+        <v>0.021343146274149034</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>0.02281508739650414</v>
+      </c>
+      <c r="Z22" s="5">
+        <v>0.022263109475620976</v>
       </c>
     </row>
   </sheetData>
@@ -4049,13 +4220,13 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C2" s="2">
-        <v>13.947368421052632</v>
+        <v>14.0</v>
       </c>
       <c r="D2" s="2">
-        <v>14.076923076923077</v>
+        <v>14.142857142857142</v>
       </c>
       <c r="E2" s="2">
         <v>13.666666666666666</v>
@@ -4068,13 +4239,13 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C3" s="2">
-        <v>15.263157894736842</v>
+        <v>15.05</v>
       </c>
       <c r="D3" s="2">
-        <v>15.23076923076923</v>
+        <v>14.928571428571429</v>
       </c>
       <c r="E3" s="2">
         <v>15.333333333333334</v>
@@ -4087,13 +4258,13 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="C4" s="2">
-        <v>14.31578947368421</v>
+        <v>14.5</v>
       </c>
       <c r="D4" s="2">
-        <v>15.615384615384615</v>
+        <v>15.785714285714286</v>
       </c>
       <c r="E4" s="2">
         <v>11.5</v>
@@ -4106,13 +4277,13 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="C5" s="2">
-        <v>17.42105263157895</v>
+        <v>17.45</v>
       </c>
       <c r="D5" s="2">
-        <v>20.46153846153846</v>
+        <v>20.285714285714285</v>
       </c>
       <c r="E5" s="2">
         <v>10.833333333333334</v>
@@ -4125,13 +4296,13 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>572</v>
+        <v>591</v>
       </c>
       <c r="C6" s="2">
-        <v>30.105263157894736</v>
+        <v>29.55</v>
       </c>
       <c r="D6" s="2">
-        <v>31.692307692307693</v>
+        <v>30.785714285714285</v>
       </c>
       <c r="E6" s="2">
         <v>26.666666666666668</v>
@@ -4144,13 +4315,13 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>899</v>
+        <v>953</v>
       </c>
       <c r="C7" s="2">
-        <v>47.31578947368421</v>
+        <v>47.65</v>
       </c>
       <c r="D7" s="2">
-        <v>46.38461538461539</v>
+        <v>46.92857142857143</v>
       </c>
       <c r="E7" s="2">
         <v>49.333333333333336</v>
@@ -4163,13 +4334,13 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>991</v>
+        <v>1041</v>
       </c>
       <c r="C8" s="2">
-        <v>52.1578947368421</v>
+        <v>52.05</v>
       </c>
       <c r="D8" s="2">
-        <v>50.38461538461539</v>
+        <v>50.357142857142854</v>
       </c>
       <c r="E8" s="2">
         <v>56.0</v>
@@ -4182,13 +4353,13 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>798</v>
+        <v>836</v>
       </c>
       <c r="C9" s="2">
-        <v>42.0</v>
+        <v>41.8</v>
       </c>
       <c r="D9" s="2">
-        <v>41.15384615384615</v>
+        <v>40.92857142857143</v>
       </c>
       <c r="E9" s="2">
         <v>43.833333333333336</v>
@@ -4201,13 +4372,13 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>767</v>
+        <v>811</v>
       </c>
       <c r="C10" s="2">
-        <v>40.36842105263158</v>
+        <v>40.55</v>
       </c>
       <c r="D10" s="2">
-        <v>39.07692307692308</v>
+        <v>39.42857142857143</v>
       </c>
       <c r="E10" s="2">
         <v>43.166666666666664</v>
@@ -4220,13 +4391,13 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>564</v>
+        <v>596</v>
       </c>
       <c r="C11" s="2">
-        <v>29.68421052631579</v>
+        <v>29.8</v>
       </c>
       <c r="D11" s="2">
-        <v>30.307692307692307</v>
+        <v>30.428571428571427</v>
       </c>
       <c r="E11" s="2">
         <v>28.333333333333332</v>
@@ -4239,13 +4410,13 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="C12" s="2">
-        <v>26.94736842105263</v>
+        <v>26.85</v>
       </c>
       <c r="D12" s="2">
-        <v>25.076923076923077</v>
+        <v>25.071428571428573</v>
       </c>
       <c r="E12" s="2">
         <v>31.0</v>
@@ -4258,13 +4429,13 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C13" s="2">
-        <v>23.31578947368421</v>
+        <v>22.65</v>
       </c>
       <c r="D13" s="2">
-        <v>20.307692307692307</v>
+        <v>19.571428571428573</v>
       </c>
       <c r="E13" s="2">
         <v>29.833333333333332</v>
@@ -4277,13 +4448,13 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C14" s="2">
-        <v>19.0</v>
+        <v>19.05</v>
       </c>
       <c r="D14" s="2">
-        <v>16.53846153846154</v>
+        <v>16.785714285714285</v>
       </c>
       <c r="E14" s="2">
         <v>24.333333333333332</v>
@@ -4296,13 +4467,13 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C15" s="2">
-        <v>16.42105263157895</v>
+        <v>16.65</v>
       </c>
       <c r="D15" s="2">
-        <v>16.0</v>
+        <v>16.357142857142858</v>
       </c>
       <c r="E15" s="2">
         <v>17.333333333333332</v>
@@ -4315,13 +4486,13 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="C16" s="2">
-        <v>19.105263157894736</v>
+        <v>19.0</v>
       </c>
       <c r="D16" s="2">
-        <v>18.46153846153846</v>
+        <v>18.357142857142858</v>
       </c>
       <c r="E16" s="2">
         <v>20.5</v>
@@ -4334,13 +4505,13 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="C17" s="2">
-        <v>17.42105263157895</v>
+        <v>17.75</v>
       </c>
       <c r="D17" s="2">
-        <v>16.23076923076923</v>
+        <v>16.785714285714285</v>
       </c>
       <c r="E17" s="2">
         <v>20.0</v>
@@ -4353,13 +4524,13 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="C18" s="2">
-        <v>21.63157894736842</v>
+        <v>21.65</v>
       </c>
       <c r="D18" s="2">
-        <v>20.76923076923077</v>
+        <v>20.857142857142858</v>
       </c>
       <c r="E18" s="2">
         <v>23.5</v>
@@ -4372,13 +4543,13 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C19" s="2">
-        <v>20.526315789473685</v>
+        <v>20.55</v>
       </c>
       <c r="D19" s="2">
-        <v>21.53846153846154</v>
+        <v>21.5</v>
       </c>
       <c r="E19" s="2">
         <v>18.333333333333332</v>
@@ -4391,13 +4562,13 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C20" s="2">
-        <v>14.789473684210526</v>
+        <v>15.2</v>
       </c>
       <c r="D20" s="2">
-        <v>16.076923076923077</v>
+        <v>16.571428571428573</v>
       </c>
       <c r="E20" s="2">
         <v>12.0</v>
@@ -4410,13 +4581,13 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="C21" s="2">
-        <v>15.105263157894736</v>
+        <v>15.2</v>
       </c>
       <c r="D21" s="2">
-        <v>13.153846153846153</v>
+        <v>13.428571428571429</v>
       </c>
       <c r="E21" s="2">
         <v>19.333333333333332</v>
@@ -4429,13 +4600,13 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2">
-        <v>10.68421052631579</v>
+        <v>10.45</v>
       </c>
       <c r="D22" s="2">
-        <v>10.461538461538462</v>
+        <v>10.142857142857142</v>
       </c>
       <c r="E22" s="2">
         <v>11.166666666666666</v>
@@ -4448,13 +4619,13 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2">
-        <v>11.789473684210526</v>
+        <v>11.6</v>
       </c>
       <c r="D23" s="2">
-        <v>10.538461538461538</v>
+        <v>10.357142857142858</v>
       </c>
       <c r="E23" s="2">
         <v>14.5</v>
@@ -4467,13 +4638,13 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2">
-        <v>12.368421052631579</v>
+        <v>12.4</v>
       </c>
       <c r="D24" s="2">
-        <v>12.76923076923077</v>
+        <v>12.785714285714286</v>
       </c>
       <c r="E24" s="2">
         <v>11.5</v>
@@ -4486,13 +4657,13 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2">
-        <v>12.31578947368421</v>
+        <v>12.1</v>
       </c>
       <c r="D25" s="2">
-        <v>14.307692307692308</v>
+        <v>13.857142857142858</v>
       </c>
       <c r="E25" s="2">
         <v>8.0</v>
@@ -4505,13 +4676,13 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <v>10336</v>
+        <v>10870</v>
       </c>
       <c r="C26" s="5">
-        <v>544.0</v>
+        <v>543.5</v>
       </c>
       <c r="D26" s="5">
-        <v>536.6153846153846</v>
+        <v>536.4285714285714</v>
       </c>
       <c r="E26" s="5">
         <v>560.0</v>
@@ -4596,10 +4767,10 @@
         <v>29</v>
       </c>
       <c r="E2" s="2">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="F2" s="2">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
@@ -4664,10 +4835,10 @@
         <v>30</v>
       </c>
       <c r="E4" s="2">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="F4" s="2">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
@@ -4698,10 +4869,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="2">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="F5" s="2">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
@@ -4715,12 +4886,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -4729,32 +4900,32 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2">
-        <v>11.7</v>
+        <v>16.8</v>
       </c>
       <c r="F6" s="2">
-        <v>3.29</v>
+        <v>-3.37</v>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H6" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -4763,21 +4934,21 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2">
-        <v>16.2</v>
+        <v>11.8</v>
       </c>
       <c r="F7" s="2">
-        <v>-3.28</v>
+        <v>3.27</v>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H7" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4800,10 +4971,10 @@
         <v>27</v>
       </c>
       <c r="E8" s="2">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="F8" s="2">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
@@ -4817,12 +4988,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -4831,13 +5002,13 @@
         </is>
       </c>
       <c r="D9" s="2">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2">
-        <v>14.4</v>
+        <v>27.3</v>
       </c>
       <c r="F9" s="2">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
@@ -4845,40 +5016,6 @@
         </is>
       </c>
       <c r="H9" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>43</v>
-      </c>
-      <c r="E10" s="2">
-        <v>27.2</v>
-      </c>
-      <c r="F10" s="2">
-        <v>3.04</v>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5302,19 +5439,40 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>23</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.04307116104868914</v>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="E20" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="5">
-        <v>705</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.06820820433436532</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="B21" s="5">
+        <v>728</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.06697332106715731</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
     </row>
   </sheetData>
 </worksheet>

--- a/reports/hourly_tracking.xlsx
+++ b/reports/hourly_tracking.xlsx
@@ -176,7 +176,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -199,7 +199,7 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>10870</v>
+        <v>11411</v>
       </c>
     </row>
     <row r="12">
@@ -221,7 +221,7 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>728 (6.7%)</t>
+          <t>766 (6.7%)</t>
         </is>
       </c>
     </row>
@@ -233,7 +233,7 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>8 of 480</t>
+          <t>7 of 504</t>
         </is>
       </c>
     </row>
@@ -245,7 +245,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>1.25 (1.00 = independent arrivals)</t>
+          <t>1.24 (1.00 = independent arrivals)</t>
         </is>
       </c>
     </row>
@@ -2163,86 +2163,173 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="C22" s="2">
+        <v>541</v>
+      </c>
+      <c r="D22" s="2">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2">
+        <v>21</v>
+      </c>
+      <c r="G22" s="2">
+        <v>39</v>
+      </c>
+      <c r="H22" s="2">
+        <v>19</v>
+      </c>
+      <c r="I22" s="2">
+        <v>46</v>
+      </c>
+      <c r="J22" s="2">
+        <v>32</v>
+      </c>
+      <c r="K22" s="2">
+        <v>43</v>
+      </c>
+      <c r="L22" s="2">
+        <v>38</v>
+      </c>
+      <c r="M22" s="2">
+        <v>34</v>
+      </c>
+      <c r="N22" s="2">
+        <v>27</v>
+      </c>
+      <c r="O22" s="2">
+        <v>24</v>
+      </c>
+      <c r="P22" s="2">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>13</v>
+      </c>
+      <c r="R22" s="2">
+        <v>21</v>
+      </c>
+      <c r="S22" s="2">
+        <v>16</v>
+      </c>
+      <c r="T22" s="2">
+        <v>20</v>
+      </c>
+      <c r="U22" s="2">
+        <v>16</v>
+      </c>
+      <c r="V22" s="2">
+        <v>17</v>
+      </c>
+      <c r="W22" s="2">
+        <v>14</v>
+      </c>
+      <c r="X22" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5">
-        <v>10870</v>
-      </c>
-      <c r="D22" s="5">
-        <v>280</v>
-      </c>
-      <c r="E22" s="5">
-        <v>301</v>
-      </c>
-      <c r="F22" s="5">
-        <v>290</v>
-      </c>
-      <c r="G22" s="5">
-        <v>349</v>
-      </c>
-      <c r="H22" s="5">
-        <v>591</v>
-      </c>
-      <c r="I22" s="5">
-        <v>953</v>
-      </c>
-      <c r="J22" s="5">
-        <v>1041</v>
-      </c>
-      <c r="K22" s="5">
-        <v>836</v>
-      </c>
-      <c r="L22" s="5">
-        <v>811</v>
-      </c>
-      <c r="M22" s="5">
-        <v>596</v>
-      </c>
-      <c r="N22" s="5">
-        <v>537</v>
-      </c>
-      <c r="O22" s="5">
+      <c r="B23" s="4"/>
+      <c r="C23" s="5">
+        <v>11411</v>
+      </c>
+      <c r="D23" s="5">
+        <v>287</v>
+      </c>
+      <c r="E23" s="5">
+        <v>309</v>
+      </c>
+      <c r="F23" s="5">
+        <v>311</v>
+      </c>
+      <c r="G23" s="5">
+        <v>388</v>
+      </c>
+      <c r="H23" s="5">
+        <v>610</v>
+      </c>
+      <c r="I23" s="5">
+        <v>999</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1073</v>
+      </c>
+      <c r="K23" s="5">
+        <v>879</v>
+      </c>
+      <c r="L23" s="5">
+        <v>849</v>
+      </c>
+      <c r="M23" s="5">
+        <v>630</v>
+      </c>
+      <c r="N23" s="5">
+        <v>564</v>
+      </c>
+      <c r="O23" s="5">
+        <v>477</v>
+      </c>
+      <c r="P23" s="5">
+        <v>407</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>346</v>
+      </c>
+      <c r="R23" s="5">
+        <v>401</v>
+      </c>
+      <c r="S23" s="5">
+        <v>371</v>
+      </c>
+      <c r="T23" s="5">
         <v>453</v>
       </c>
-      <c r="P22" s="5">
-        <v>381</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>333</v>
-      </c>
-      <c r="R22" s="5">
-        <v>380</v>
-      </c>
-      <c r="S22" s="5">
-        <v>355</v>
-      </c>
-      <c r="T22" s="5">
-        <v>433</v>
-      </c>
-      <c r="U22" s="5">
-        <v>411</v>
-      </c>
-      <c r="V22" s="5">
-        <v>304</v>
-      </c>
-      <c r="W22" s="5">
-        <v>304</v>
-      </c>
-      <c r="X22" s="5">
-        <v>209</v>
-      </c>
-      <c r="Y22" s="5">
-        <v>232</v>
-      </c>
-      <c r="Z22" s="5">
-        <v>248</v>
-      </c>
-      <c r="AA22" s="5">
-        <v>242</v>
+      <c r="U23" s="5">
+        <v>427</v>
+      </c>
+      <c r="V23" s="5">
+        <v>321</v>
+      </c>
+      <c r="W23" s="5">
+        <v>318</v>
+      </c>
+      <c r="X23" s="5">
+        <v>228</v>
+      </c>
+      <c r="Y23" s="5">
+        <v>250</v>
+      </c>
+      <c r="Z23" s="5">
+        <v>257</v>
+      </c>
+      <c r="AA23" s="5">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -4093,83 +4180,167 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>weekday</t>
+        </is>
+      </c>
+      <c r="C22" s="3">
+        <v>0.012939001848428836</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.014787430683918669</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.038817005545286505</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.07208872458410351</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.03512014787430684</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.08502772643253234</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0.059149722735674676</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.07948243992606285</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0.07024029574861368</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0.06284658040665435</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0.04990757855822551</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0.04436229205175601</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0.04805914972273567</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0.024029574861367836</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0.038817005545286505</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0.029574861367837338</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0.036968576709796676</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0.029574861367837338</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0.031423290203327174</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0.025878003696857672</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0.03512014787430684</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0.033271719038817</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0.0166358595194085</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0.025878003696857672</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5">
-        <v>0.025758969641214352</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0.027690892364305428</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0.02667893284268629</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0.03210671573137074</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0.05436982520699172</v>
-      </c>
-      <c r="H22" s="5">
-        <v>0.08767249310027599</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0.09576816927322906</v>
-      </c>
-      <c r="J22" s="5">
-        <v>0.07690892364305428</v>
-      </c>
-      <c r="K22" s="5">
-        <v>0.07460901563937443</v>
-      </c>
-      <c r="L22" s="5">
-        <v>0.05482980680772769</v>
-      </c>
-      <c r="M22" s="5">
-        <v>0.04940202391904324</v>
-      </c>
-      <c r="N22" s="5">
-        <v>0.04167433302667893</v>
-      </c>
-      <c r="O22" s="5">
-        <v>0.035050597976080955</v>
-      </c>
-      <c r="P22" s="5">
-        <v>0.03063477460901564</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>0.034958601655933765</v>
-      </c>
-      <c r="R22" s="5">
-        <v>0.03265869365225391</v>
-      </c>
-      <c r="S22" s="5">
-        <v>0.03983440662373505</v>
-      </c>
-      <c r="T22" s="5">
-        <v>0.03781048758049678</v>
-      </c>
-      <c r="U22" s="5">
-        <v>0.02796688132474701</v>
-      </c>
-      <c r="V22" s="5">
-        <v>0.02796688132474701</v>
-      </c>
-      <c r="W22" s="5">
-        <v>0.01922723091076357</v>
-      </c>
-      <c r="X22" s="5">
-        <v>0.021343146274149034</v>
-      </c>
-      <c r="Y22" s="5">
-        <v>0.02281508739650414</v>
-      </c>
-      <c r="Z22" s="5">
-        <v>0.022263109475620976</v>
+      <c r="B23" s="4"/>
+      <c r="C23" s="5">
+        <v>0.025151169923757776</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.027079134168784505</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.027254403645605118</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.03400227850319867</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0.053457190430286565</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0.08754710367189554</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0.09403207431425817</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0.07703093506265883</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0.07440189291034967</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0.05520988519849268</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0.0494259924634125</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0.04180177022171589</v>
+      </c>
+      <c r="O23" s="5">
+        <v>0.03566733853299448</v>
+      </c>
+      <c r="P23" s="5">
+        <v>0.030321619489965822</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>0.035141530102532646</v>
+      </c>
+      <c r="R23" s="5">
+        <v>0.03251248795022347</v>
+      </c>
+      <c r="S23" s="5">
+        <v>0.03969853649986855</v>
+      </c>
+      <c r="T23" s="5">
+        <v>0.0374200333012006</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0.028130751029708176</v>
+      </c>
+      <c r="V23" s="5">
+        <v>0.027867846814477258</v>
+      </c>
+      <c r="W23" s="5">
+        <v>0.019980720357549733</v>
+      </c>
+      <c r="X23" s="5">
+        <v>0.021908684602576462</v>
+      </c>
+      <c r="Y23" s="5">
+        <v>0.022522127771448602</v>
+      </c>
+      <c r="Z23" s="5">
+        <v>0.022434493033038298</v>
       </c>
     </row>
   </sheetData>
@@ -4220,13 +4391,13 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C2" s="2">
-        <v>14.0</v>
+        <v>13.666666666666666</v>
       </c>
       <c r="D2" s="2">
-        <v>14.142857142857142</v>
+        <v>13.666666666666666</v>
       </c>
       <c r="E2" s="2">
         <v>13.666666666666666</v>
@@ -4239,13 +4410,13 @@
         </is>
       </c>
       <c r="B3" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C3" s="2">
-        <v>15.05</v>
+        <v>14.714285714285714</v>
       </c>
       <c r="D3" s="2">
-        <v>14.928571428571429</v>
+        <v>14.466666666666667</v>
       </c>
       <c r="E3" s="2">
         <v>15.333333333333334</v>
@@ -4258,13 +4429,13 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C4" s="2">
-        <v>14.5</v>
+        <v>14.80952380952381</v>
       </c>
       <c r="D4" s="2">
-        <v>15.785714285714286</v>
+        <v>16.133333333333333</v>
       </c>
       <c r="E4" s="2">
         <v>11.5</v>
@@ -4277,13 +4448,13 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="C5" s="2">
-        <v>17.45</v>
+        <v>18.476190476190474</v>
       </c>
       <c r="D5" s="2">
-        <v>20.285714285714285</v>
+        <v>21.533333333333335</v>
       </c>
       <c r="E5" s="2">
         <v>10.833333333333334</v>
@@ -4296,13 +4467,13 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="C6" s="2">
-        <v>29.55</v>
+        <v>29.047619047619047</v>
       </c>
       <c r="D6" s="2">
-        <v>30.785714285714285</v>
+        <v>30.0</v>
       </c>
       <c r="E6" s="2">
         <v>26.666666666666668</v>
@@ -4315,13 +4486,13 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <v>953</v>
+        <v>999</v>
       </c>
       <c r="C7" s="2">
-        <v>47.65</v>
+        <v>47.57142857142857</v>
       </c>
       <c r="D7" s="2">
-        <v>46.92857142857143</v>
+        <v>46.86666666666667</v>
       </c>
       <c r="E7" s="2">
         <v>49.333333333333336</v>
@@ -4334,13 +4505,13 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>1041</v>
+        <v>1073</v>
       </c>
       <c r="C8" s="2">
-        <v>52.05</v>
+        <v>51.095238095238095</v>
       </c>
       <c r="D8" s="2">
-        <v>50.357142857142854</v>
+        <v>49.13333333333333</v>
       </c>
       <c r="E8" s="2">
         <v>56.0</v>
@@ -4353,13 +4524,13 @@
         </is>
       </c>
       <c r="B9" s="2">
-        <v>836</v>
+        <v>879</v>
       </c>
       <c r="C9" s="2">
-        <v>41.8</v>
+        <v>41.857142857142854</v>
       </c>
       <c r="D9" s="2">
-        <v>40.92857142857143</v>
+        <v>41.06666666666667</v>
       </c>
       <c r="E9" s="2">
         <v>43.833333333333336</v>
@@ -4372,13 +4543,13 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <v>811</v>
+        <v>849</v>
       </c>
       <c r="C10" s="2">
-        <v>40.55</v>
+        <v>40.42857142857143</v>
       </c>
       <c r="D10" s="2">
-        <v>39.42857142857143</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="E10" s="2">
         <v>43.166666666666664</v>
@@ -4391,13 +4562,13 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>596</v>
+        <v>630</v>
       </c>
       <c r="C11" s="2">
-        <v>29.8</v>
+        <v>30.0</v>
       </c>
       <c r="D11" s="2">
-        <v>30.428571428571427</v>
+        <v>30.666666666666668</v>
       </c>
       <c r="E11" s="2">
         <v>28.333333333333332</v>
@@ -4410,13 +4581,13 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="C12" s="2">
-        <v>26.85</v>
+        <v>26.857142857142858</v>
       </c>
       <c r="D12" s="2">
-        <v>25.071428571428573</v>
+        <v>25.2</v>
       </c>
       <c r="E12" s="2">
         <v>31.0</v>
@@ -4429,13 +4600,13 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="C13" s="2">
-        <v>22.65</v>
+        <v>22.714285714285715</v>
       </c>
       <c r="D13" s="2">
-        <v>19.571428571428573</v>
+        <v>19.866666666666667</v>
       </c>
       <c r="E13" s="2">
         <v>29.833333333333332</v>
@@ -4448,13 +4619,13 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="C14" s="2">
-        <v>19.05</v>
+        <v>19.38095238095238</v>
       </c>
       <c r="D14" s="2">
-        <v>16.785714285714285</v>
+        <v>17.4</v>
       </c>
       <c r="E14" s="2">
         <v>24.333333333333332</v>
@@ -4467,13 +4638,13 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C15" s="2">
-        <v>16.65</v>
+        <v>16.476190476190474</v>
       </c>
       <c r="D15" s="2">
-        <v>16.357142857142858</v>
+        <v>16.133333333333333</v>
       </c>
       <c r="E15" s="2">
         <v>17.333333333333332</v>
@@ -4486,13 +4657,13 @@
         </is>
       </c>
       <c r="B16" s="2">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="C16" s="2">
-        <v>19.0</v>
+        <v>19.095238095238095</v>
       </c>
       <c r="D16" s="2">
-        <v>18.357142857142858</v>
+        <v>18.533333333333335</v>
       </c>
       <c r="E16" s="2">
         <v>20.5</v>
@@ -4505,13 +4676,13 @@
         </is>
       </c>
       <c r="B17" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C17" s="2">
-        <v>17.75</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="D17" s="2">
-        <v>16.785714285714285</v>
+        <v>16.733333333333334</v>
       </c>
       <c r="E17" s="2">
         <v>20.0</v>
@@ -4524,13 +4695,13 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C18" s="2">
-        <v>21.65</v>
+        <v>21.571428571428573</v>
       </c>
       <c r="D18" s="2">
-        <v>20.857142857142858</v>
+        <v>20.8</v>
       </c>
       <c r="E18" s="2">
         <v>23.5</v>
@@ -4543,13 +4714,13 @@
         </is>
       </c>
       <c r="B19" s="2">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="C19" s="2">
-        <v>20.55</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="D19" s="2">
-        <v>21.5</v>
+        <v>21.133333333333333</v>
       </c>
       <c r="E19" s="2">
         <v>18.333333333333332</v>
@@ -4562,13 +4733,13 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="C20" s="2">
-        <v>15.2</v>
+        <v>15.285714285714286</v>
       </c>
       <c r="D20" s="2">
-        <v>16.571428571428573</v>
+        <v>16.6</v>
       </c>
       <c r="E20" s="2">
         <v>12.0</v>
@@ -4581,13 +4752,13 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C21" s="2">
-        <v>15.2</v>
+        <v>15.142857142857142</v>
       </c>
       <c r="D21" s="2">
-        <v>13.428571428571429</v>
+        <v>13.466666666666667</v>
       </c>
       <c r="E21" s="2">
         <v>19.333333333333332</v>
@@ -4600,13 +4771,13 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2">
-        <v>10.45</v>
+        <v>10.857142857142858</v>
       </c>
       <c r="D22" s="2">
-        <v>10.142857142857142</v>
+        <v>10.733333333333333</v>
       </c>
       <c r="E22" s="2">
         <v>11.166666666666666</v>
@@ -4619,13 +4790,13 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="C23" s="2">
-        <v>11.6</v>
+        <v>11.904761904761905</v>
       </c>
       <c r="D23" s="2">
-        <v>10.357142857142858</v>
+        <v>10.866666666666667</v>
       </c>
       <c r="E23" s="2">
         <v>14.5</v>
@@ -4638,13 +4809,13 @@
         </is>
       </c>
       <c r="B24" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C24" s="2">
-        <v>12.4</v>
+        <v>12.238095238095237</v>
       </c>
       <c r="D24" s="2">
-        <v>12.785714285714286</v>
+        <v>12.533333333333333</v>
       </c>
       <c r="E24" s="2">
         <v>11.5</v>
@@ -4657,13 +4828,13 @@
         </is>
       </c>
       <c r="B25" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2">
-        <v>12.1</v>
+        <v>12.19047619047619</v>
       </c>
       <c r="D25" s="2">
-        <v>13.857142857142858</v>
+        <v>13.866666666666667</v>
       </c>
       <c r="E25" s="2">
         <v>8.0</v>
@@ -4676,13 +4847,13 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <v>10870</v>
+        <v>11411</v>
       </c>
       <c r="C26" s="5">
-        <v>543.5</v>
+        <v>543.3809523809522</v>
       </c>
       <c r="D26" s="5">
-        <v>536.4285714285714</v>
+        <v>536.7333333333333</v>
       </c>
       <c r="E26" s="5">
         <v>560.0</v>
@@ -4767,10 +4938,10 @@
         <v>29</v>
       </c>
       <c r="E2" s="2">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F2" s="2">
-        <v>4.65</v>
+        <v>4.79</v>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
@@ -4835,10 +5006,10 @@
         <v>30</v>
       </c>
       <c r="E4" s="2">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="F4" s="2">
-        <v>3.96</v>
+        <v>4.16</v>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
@@ -4869,10 +5040,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="2">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="F5" s="2">
-        <v>3.57</v>
+        <v>3.37</v>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
@@ -4906,7 +5077,7 @@
         <v>16.8</v>
       </c>
       <c r="F6" s="2">
-        <v>-3.37</v>
+        <v>-3.36</v>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
@@ -4937,10 +5108,10 @@
         <v>23</v>
       </c>
       <c r="E7" s="2">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="F7" s="2">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
@@ -4971,10 +5142,10 @@
         <v>27</v>
       </c>
       <c r="E8" s="2">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="F8" s="2">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
@@ -4982,40 +5153,6 @@
         </is>
       </c>
       <c r="H8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2">
-        <v>27.3</v>
-      </c>
-      <c r="F9" s="2">
-        <v>3.01</v>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5460,19 +5597,40 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B21" s="2">
+        <v>38</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.07024029574861368</v>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="E21" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="5">
-        <v>728</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.06697332106715731</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="B22" s="5">
+        <v>766</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.06712820962229428</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
     </row>
   </sheetData>
 </worksheet>
